--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_09/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_09/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>59.47</v>
+        <v>61.75</v>
       </c>
       <c r="D2" t="n">
-        <v>20.42</v>
+        <v>19.56</v>
       </c>
       <c r="E2" t="n">
-        <v>34.33</v>
+        <v>31.68</v>
       </c>
       <c r="F2" t="n">
-        <v>36.98</v>
+        <v>38.71</v>
       </c>
       <c r="G2" t="n">
-        <v>41.87</v>
+        <v>45.26</v>
       </c>
       <c r="H2" t="n">
-        <v>51.96</v>
+        <v>57.11</v>
       </c>
       <c r="I2" t="n">
-        <v>75.65000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>63.02</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>45.99</v>
+        <v>42.77</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25</v>
+        <v>4.45</v>
       </c>
       <c r="E3" t="n">
-        <v>0.53</v>
+        <v>10.39</v>
       </c>
       <c r="F3" t="n">
-        <v>45.92</v>
+        <v>35.5</v>
       </c>
       <c r="G3" t="n">
-        <v>45.92</v>
+        <v>40.03</v>
       </c>
       <c r="H3" t="n">
-        <v>45.93</v>
+        <v>45.91</v>
       </c>
       <c r="I3" t="n">
-        <v>45.93</v>
+        <v>46.03</v>
       </c>
       <c r="J3" t="n">
-        <v>47.52</v>
+        <v>48.08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>7.74</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.16</v>
+        <v>2.27</v>
       </c>
       <c r="E4" t="n">
-        <v>14.96</v>
+        <v>26.33</v>
       </c>
       <c r="F4" t="n">
-        <v>5.62</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="H4" t="n">
-        <v>7.39</v>
+        <v>9.34</v>
       </c>
       <c r="I4" t="n">
-        <v>8.83</v>
+        <v>10.67</v>
       </c>
       <c r="J4" t="n">
-        <v>10.38</v>
+        <v>11.51</v>
       </c>
       <c r="K4" t="n">
-        <v>4.76</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>106.77</v>
+        <v>143.66</v>
       </c>
       <c r="D5" t="n">
-        <v>9.15</v>
+        <v>52.54</v>
       </c>
       <c r="E5" t="n">
-        <v>8.57</v>
+        <v>36.57</v>
       </c>
       <c r="F5" t="n">
-        <v>79.65000000000001</v>
+        <v>52.82</v>
       </c>
       <c r="G5" t="n">
-        <v>102.26</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>106.09</v>
+        <v>169.32</v>
       </c>
       <c r="I5" t="n">
-        <v>111.6</v>
+        <v>179.3</v>
       </c>
       <c r="J5" t="n">
-        <v>134.79</v>
+        <v>193.6</v>
       </c>
       <c r="K5" t="n">
-        <v>55.13</v>
+        <v>140.78</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.77</v>
+        <v>4.54</v>
       </c>
       <c r="D6" t="n">
-        <v>0.26</v>
+        <v>0.84</v>
       </c>
       <c r="E6" t="n">
-        <v>5.53</v>
+        <v>18.46</v>
       </c>
       <c r="F6" t="n">
-        <v>3.71</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="H6" t="n">
-        <v>4.84</v>
+        <v>4.82</v>
       </c>
       <c r="I6" t="n">
-        <v>4.93</v>
+        <v>4.95</v>
       </c>
       <c r="J6" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.29</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
